--- a/output/pdf_financials_xlsx/ITR.xlsx
+++ b/output/pdf_financials_xlsx/ITR.xlsx
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.209038</v>
+        <v>-0.209038</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-8.464819</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.209038</v>
+        <v>-0.209038</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-8.464819</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.209038</v>
+        <v>-0.209038</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-8.464819</v>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.209038</v>
+        <v>-0.209038</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-8.464819</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.209038</v>
+        <v>-0.209038</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-8.464819</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5617,7 +5617,7 @@
         <v>21.775</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="92">
@@ -5630,40 +5630,40 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.93162</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.987382</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.554104</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.186287</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.140664</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.124353</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.364642</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>8.853999999999999</v>
@@ -5672,7 +5672,7 @@
         <v>9.895</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>11.304</v>
       </c>
     </row>
     <row r="93">
@@ -7024,16 +7024,16 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>6.981</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.00625</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -10496,7 +10496,11 @@
           <t>Share-based payment reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -10586,7 +10590,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10678,7 +10686,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -15896,7 +15908,11 @@
           <t>Reserves (Note 18)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -18956,7 +18972,11 @@
           <t>Reserves (Note 16) 7,124,353</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -20294,7 +20314,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -23468,7 +23492,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -24510,7 +24538,11 @@
           <t>Reserve for warrants (Note 13)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -25262,7 +25294,11 @@
           <t>Reserve for warrants (Note 13)</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -26226,7 +26262,11 @@
           <t>Reserve for warrants (Note 15)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -27300,7 +27340,11 @@
           <t>Reserve for warrants (Note 16) 252,000</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -44950,7 +44994,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -46008,7 +46056,11 @@
           <t>Shares received for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -63288,7 +63340,7 @@
         </is>
       </c>
       <c r="E583" s="5" t="n">
-        <v>0.209038</v>
+        <v>-0.209038</v>
       </c>
       <c r="F583" s="5" t="n">
         <v>-8.464819</v>

--- a/output/pdf_financials_xlsx/ITR.xlsx
+++ b/output/pdf_financials_xlsx/ITR.xlsx
@@ -1024,31 +1024,31 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.009219</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.141683</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.230034</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.203887</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.039725</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.272005</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.800699</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.669</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2.485</v>
       </c>
     </row>
     <row r="13">
@@ -1953,31 +1953,31 @@
         <v>0.342026</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.523877</v>
+        <v>-5.533096</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-14.807839</v>
+        <v>-14.949522</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-21.653049</v>
+        <v>-21.883083</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-20.249424</v>
+        <v>-20.453311</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-32.933645</v>
+        <v>-32.97337</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-19.807021</v>
+        <v>-20.079026</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-29.016</v>
+        <v>-29.816699</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-8.765000000000001</v>
+        <v>-9.433999999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>19.063</v>
+        <v>16.578</v>
       </c>
     </row>
     <row r="28">
@@ -2063,31 +2063,31 @@
         <v>0.342026</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.521553</v>
+        <v>-5.530772</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-14.807839</v>
+        <v>-14.949522</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-21.653049</v>
+        <v>-21.883083</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-20.249424</v>
+        <v>-20.453311</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-32.933645</v>
+        <v>-32.97337</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-19.807021</v>
+        <v>-20.079026</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-27.97</v>
+        <v>-28.770699</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.906</v>
+        <v>-7.575</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.955</v>
+        <v>31.47</v>
       </c>
     </row>
     <row r="30">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-22.75453047775947</v>
+        <v>-24.95881383855025</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>13.92020530816723</v>
+        <v>12.90145371957069</v>
       </c>
     </row>
     <row r="31">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.05706</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.595409</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.10682</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.05706</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.595409</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.10682</v>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.112119</v>
+        <v>0.055059</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.70418</v>
+        <v>0.108771</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.04841</v>
@@ -7394,10 +7394,10 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.478</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-2.358</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7449,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.478</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-2.358</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
@@ -33384,7 +33384,11 @@
           <t>Principal lease payments 13</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -49828,7 +49832,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -53972,7 +53976,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -56896,7 +56900,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">

--- a/output/pdf_financials_xlsx/ITR.xlsx
+++ b/output/pdf_financials_xlsx/ITR.xlsx
@@ -1097,10 +1097,10 @@
         <v>-0</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>1.871</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>2.739</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>-0</v>
@@ -1971,10 +1971,10 @@
         <v>-20.079026</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-29.816699</v>
+        <v>-31.687699</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-9.433999999999999</v>
+        <v>-12.173</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>16.578</v>
@@ -2011,22 +2011,22 @@
         <v>0.002324</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.315478</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.454732</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.607859</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.927957</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.968645</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1.046</v>
+        <v>1.046095</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>1.859</v>
@@ -2066,25 +2066,25 @@
         <v>-5.530772</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-14.949522</v>
+        <v>-14.634044</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-21.883083</v>
+        <v>-21.428351</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-20.453311</v>
+        <v>-19.845452</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-32.97337</v>
+        <v>-32.045413</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-20.079026</v>
+        <v>-19.110381</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-28.770699</v>
+        <v>-30.641604</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-7.575</v>
+        <v>-10.314</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>31.47</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-24.95881383855025</v>
+        <v>-33.9835255354201</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>12.90145371957069</v>
@@ -6052,22 +6052,22 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.002324</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.315478</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.454732</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.607859</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.927957</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.968645</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>1.046</v>
@@ -7138,13 +7138,13 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>3.271561</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.797215</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -34158,7 +34158,11 @@
           <t>Depreciation – property, plant and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -34248,7 +34252,11 @@
           <t>Depreciation – right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -38346,7 +38354,11 @@
           <t>Depreciation – Property, plant and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -38440,7 +38452,11 @@
           <t>Depreciation – Right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -40984,7 +41000,11 @@
           <t>Depreciation – Property, plant and equipment</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -42020,7 +42040,11 @@
           <t>Depreciation – Right-of-use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -46356,7 +46380,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -48378,7 +48406,11 @@
           <t>Issuance of common shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -52048,7 +52080,11 @@
           <t>Net finance expenses 19</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -53006,7 +53042,11 @@
           <t>Depreciation – property, plant and equipment (Note 8) $</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -53058,16 +53098,16 @@
         </is>
       </c>
       <c r="O472" s="5" t="n">
-        <v>-0.30247</v>
+        <v>0.30247</v>
       </c>
       <c r="P472" s="5" t="n">
-        <v>-0.467703</v>
+        <v>0.467703</v>
       </c>
       <c r="Q472" s="5" t="n">
-        <v>-0.553002</v>
+        <v>0.553002</v>
       </c>
       <c r="R472" s="5" t="n">
-        <v>-0.592396</v>
+        <v>0.592396</v>
       </c>
       <c r="S472" t="inlineStr">
         <is>
@@ -53096,7 +53136,11 @@
           <t>Depreciation – right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -53148,16 +53192,16 @@
         </is>
       </c>
       <c r="O473" s="5" t="n">
-        <v>-0.305389</v>
+        <v>0.305389</v>
       </c>
       <c r="P473" s="5" t="n">
-        <v>-0.460254</v>
+        <v>0.460254</v>
       </c>
       <c r="Q473" s="5" t="n">
-        <v>-0.415643</v>
+        <v>0.415643</v>
       </c>
       <c r="R473" s="5" t="n">
-        <v>-0.453699</v>
+        <v>0.453699</v>
       </c>
       <c r="S473" t="inlineStr">
         <is>
@@ -56436,7 +56480,11 @@
           <t>Depreciation - Property, plant and equipment (Note 8) $</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>
@@ -56488,10 +56536,10 @@
         </is>
       </c>
       <c r="O510" s="5" t="n">
-        <v>-0.30247</v>
+        <v>0.30247</v>
       </c>
       <c r="P510" s="5" t="n">
-        <v>-0.467703</v>
+        <v>0.467703</v>
       </c>
       <c r="Q510" t="inlineStr">
         <is>
@@ -56530,7 +56578,11 @@
           <t>Depreciation - Right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -56572,16 +56624,16 @@
         </is>
       </c>
       <c r="M511" s="5" t="n">
-        <v>-0.216551</v>
+        <v>0.216551</v>
       </c>
       <c r="N511" s="5" t="n">
-        <v>-0.263162</v>
+        <v>0.263162</v>
       </c>
       <c r="O511" s="5" t="n">
-        <v>-0.305389</v>
+        <v>0.305389</v>
       </c>
       <c r="P511" s="5" t="n">
-        <v>-0.460254</v>
+        <v>0.460254</v>
       </c>
       <c r="Q511" t="inlineStr">
         <is>
@@ -58236,7 +58288,11 @@
           <t>Depreciation - Property, plant and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr">
         <is>
           <t>-</t>
@@ -58278,10 +58334,10 @@
         </is>
       </c>
       <c r="M529" s="5" t="n">
-        <v>-0.098927</v>
+        <v>0.098927</v>
       </c>
       <c r="N529" s="5" t="n">
-        <v>-0.19157</v>
+        <v>0.19157</v>
       </c>
       <c r="O529" t="inlineStr">
         <is>
@@ -58800,7 +58856,11 @@
           <t>Depreciation - Property, plant and equipment</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -58837,10 +58897,10 @@
         </is>
       </c>
       <c r="L535" s="5" t="n">
-        <v>-0.002324</v>
+        <v>0.002324</v>
       </c>
       <c r="M535" s="5" t="n">
-        <v>-0.098927</v>
+        <v>0.098927</v>
       </c>
       <c r="N535" t="inlineStr">
         <is>
@@ -58894,7 +58954,11 @@
           <t>Depreciation - Right-of-use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -58936,7 +59000,7 @@
         </is>
       </c>
       <c r="M536" s="5" t="n">
-        <v>-0.216551</v>
+        <v>0.216551</v>
       </c>
       <c r="N536" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ITR.xlsx
+++ b/output/pdf_financials_xlsx/ITR.xlsx
@@ -746,7 +746,7 @@
         <v>0.005291</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.024</v>
+        <v>0.016651</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.103793</v>
@@ -1226,16 +1226,16 @@
         <v>-0.209038</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-8.464819</v>
+        <v>-8.205819</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.754353</v>
+        <v>-1.507353</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.945908</v>
+        <v>-0.9139080000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.937107</v>
+        <v>-0.913107</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.232303</v>
@@ -1281,16 +1281,16 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.259</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.247</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.032</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.024</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1935,16 +1935,16 @@
         <v>-0.209038</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.464819</v>
+        <v>-8.205819</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.754353</v>
+        <v>-1.507353</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.945908</v>
+        <v>-0.9139080000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.937107</v>
+        <v>-0.913107</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.232303</v>
@@ -2045,16 +2045,16 @@
         <v>-0.209038</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.464819</v>
+        <v>-8.205819</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.754353</v>
+        <v>-1.507353</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.945908</v>
+        <v>-0.9139080000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.937107</v>
+        <v>-0.913107</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.232303</v>
@@ -2183,16 +2183,16 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.156296769402298</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-16.38634082394768</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.501446535099813</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.628388567823924</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -4214,34 +4214,34 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.191528</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.104401</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.552123</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.955431</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.580485</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.708</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>3.426</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>2.429</v>
       </c>
     </row>
     <row r="68">
@@ -4269,28 +4269,28 @@
         <v>0.153984</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.096945</v>
+        <v>0.152945</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.605324</v>
+        <v>0.796852</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1.204514</v>
+        <v>1.308915</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1.310553</v>
+        <v>1.862676</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>1.009048</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>2.487332</v>
+        <v>3.442763</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>2.633911</v>
+        <v>3.214396</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>4.474</v>
+        <v>5.182</v>
       </c>
       <c r="P68" s="3" t="n">
         <v>19.919</v>
@@ -4406,7 +4406,7 @@
         <v>5.237</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>7.677</v>
       </c>
     </row>
     <row r="71">
@@ -4461,7 +4461,7 @@
         <v>5.237</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>7.677</v>
       </c>
     </row>
     <row r="72">
@@ -4654,34 +4654,34 @@
         <v>1.149298</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.785986</v>
+        <v>0.729986</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.530675</v>
+        <v>2.339147</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>7.383329</v>
+        <v>7.278928</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>3.134509</v>
+        <v>2.582386</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>2.413388</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>3.231909</v>
+        <v>2.276478</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>12.756757</v>
+        <v>12.176272</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>11.835</v>
+        <v>11.127</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0.182</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>12.834</v>
+        <v>5.157</v>
       </c>
     </row>
     <row r="76">
@@ -4981,10 +4981,8 @@
       <c r="P80" s="3" t="n">
         <v>0.06673049672551798</v>
       </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q80" s="3" t="n">
+        <v>0.04144219038467767</v>
       </c>
     </row>
     <row r="81">
@@ -6461,7 +6459,7 @@
         <v>1.543</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="108">
@@ -6602,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>2.383552</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -9640,7 +9638,11 @@
           <t>Lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -28014,7 +28016,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -43192,7 +43198,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -43384,7 +43394,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -45310,7 +45324,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -60200,7 +60218,11 @@
           <t>Office expenses (Note 9)</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -63310,7 +63332,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -65862,7 +65888,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr"/>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E609" t="inlineStr">
         <is>
           <t>-</t>
@@ -66812,7 +66842,11 @@
           <t>Deferred income tax recovery (Note 18)</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
